--- a/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2022_antofagasta.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2022_antofagasta.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 18:17</t>
+    <t xml:space="preserve">2026-09-09 19:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2022_antofagasta.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2022_antofagasta.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:07</t>
+    <t xml:space="preserve">2026-09-18 09:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -520,7 +520,9 @@
       <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -532,7 +534,9 @@
       <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
@@ -544,7 +548,9 @@
       <c r="C4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
@@ -556,7 +562,9 @@
       <c r="C5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
@@ -568,7 +576,9 @@
       <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
@@ -580,7 +590,9 @@
       <c r="C7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
@@ -592,7 +604,9 @@
       <c r="C8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
@@ -604,7 +618,9 @@
       <c r="C9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
@@ -616,7 +632,9 @@
       <c r="C10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
@@ -628,7 +646,9 @@
       <c r="C11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
@@ -640,7 +660,9 @@
       <c r="C12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
@@ -652,7 +674,9 @@
       <c r="C13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
@@ -664,7 +688,9 @@
       <c r="C14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
@@ -676,7 +702,9 @@
       <c r="C15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
@@ -688,7 +716,9 @@
       <c r="C16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
@@ -700,7 +730,9 @@
       <c r="C17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" s="2" t="n">
+        <v>2.91</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D17"/>
@@ -902,13 +934,13 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="12">
@@ -916,21 +948,21 @@
         <v>2023</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2.51</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="14">
@@ -938,14 +970,25 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>2.6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
+  <autoFilter ref="A1:C15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
